--- a/samples/Sample_2_For_MBBS_College_Lecturer.xlsx
+++ b/samples/Sample_2_For_MBBS_College_Lecturer.xlsx
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ishaan Verma</t>
+          <t>Yash Joshi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ishita Gowda</t>
+          <t>Aadhya Reddy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rohan Hegde</t>
+          <t>Aarav Hegde</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Diya Kulkarni</t>
+          <t>Riya Rao</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aditya Sharma</t>
+          <t>Vivaan Iyer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tanya Joshi</t>
+          <t>Kritika Murthy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vikram Murthy</t>
+          <t>Ishaan Patel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aadhya Rao</t>
+          <t>Swathi Hegde</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vivaan Shetty</t>
+          <t>Nikhil Joshi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pooja Shetty</t>
+          <t>Myra Joshi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nikhil Pai</t>
+          <t>Vikram Gowda</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kritika Pai</t>
+          <t>Kritika Iyer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Karthik Prabhu</t>
+          <t>Krishna Prabhu</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Meera Sharma</t>
+          <t>Shreya Sharma</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aditya Shetty</t>
+          <t>Sameer Prabhu</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Myra Shetty</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Devansh Murthy</t>
+          <t>Nikhil Singh</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Myra Naik</t>
+          <t>Diya Patel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Arjun Pai</t>
+          <t>Krishna Desai</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Diya Prabhu</t>
+          <t>Swathi Naik</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Akash Joshi</t>
+          <t>Vihaan Gowda</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shreya Iyer</t>
+          <t>Nisha Kulkarni</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rahul Iyer</t>
+          <t>Pranav Gowda</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Neha Murthy</t>
+          <t>Shreya Pai</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Devansh Gowda</t>
+          <t>Pranav Iyer</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Anjali Murthy</t>
+          <t>Aadhya Nair</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Devansh Patel</t>
+          <t>Rahul Prabhu</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Diya Shetty</t>
+          <t>Myra Reddy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aarav Shetty</t>
+          <t>Rahul Sharma</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aadhya Reddy</t>
+          <t>Riya Joshi</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1611,29 +1611,33 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C2" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E2" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F2" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Neuroanatomy</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Head &amp; Neck</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Consistently excellent — ready for tougher challenges.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1642,26 +1646,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C3" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D3" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F3" t="n">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Thorax</t>
+          <t>Upper Limb</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -1673,24 +1677,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C4" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D4" t="n">
+        <v>83</v>
+      </c>
+      <c r="E4" t="n">
         <v>85</v>
       </c>
-      <c r="E4" t="n">
-        <v>80</v>
-      </c>
       <c r="F4" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Head &amp; Neck</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -1700,33 +1708,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D5" t="n">
         <v>53</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Neuroanatomy</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Average performance — revision of basics recommended.</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1735,19 +1735,19 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>68</v>
+      </c>
+      <c r="C6" t="n">
+        <v>63</v>
+      </c>
+      <c r="D6" t="n">
         <v>64</v>
       </c>
-      <c r="C6" t="n">
-        <v>64</v>
-      </c>
-      <c r="D6" t="n">
-        <v>70</v>
-      </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F6" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1757,11 +1757,7 @@
           <t>Head &amp; Neck</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>On track, but should aim higher with focused practice.</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1770,29 +1766,29 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>28</v>
+      </c>
+      <c r="C7" t="n">
+        <v>28</v>
+      </c>
+      <c r="D7" t="n">
         <v>29</v>
-      </c>
-      <c r="C7" t="n">
-        <v>27</v>
-      </c>
-      <c r="D7" t="n">
-        <v>34</v>
       </c>
       <c r="E7" t="n">
         <v>31</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Lower Limb</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Below expectations — recommend extra classes after school.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1801,33 +1797,29 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>47</v>
+      </c>
+      <c r="C8" t="n">
+        <v>41</v>
+      </c>
+      <c r="D8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E8" t="n">
         <v>39</v>
       </c>
-      <c r="C8" t="n">
-        <v>37</v>
-      </c>
-      <c r="D8" t="n">
-        <v>29</v>
-      </c>
-      <c r="E8" t="n">
-        <v>37</v>
-      </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Lower Limb</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Finding it difficult to keep pace, needs individual attention.</t>
-        </is>
-      </c>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1836,33 +1828,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Neuroanatomy</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Very low scores across the board, please involve parents.</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1871,24 +1855,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D10" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E10" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Thorax</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1898,19 +1886,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C11" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D11" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E11" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F11" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1929,24 +1917,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="C12" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="E12" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Lower Limb</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1956,28 +1948,24 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>65</v>
+      </c>
+      <c r="C13" t="n">
         <v>67</v>
       </c>
-      <c r="C13" t="n">
-        <v>76</v>
-      </c>
       <c r="D13" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E13" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="F13" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Neuroanatomy</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -1991,33 +1979,29 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E14" t="n">
         <v>96</v>
       </c>
       <c r="F14" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Head &amp; Neck</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Exceptional performance, keep up this standard.</t>
-        </is>
-      </c>
+          <t>Thorax</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2026,33 +2010,29 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C15" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="E15" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F15" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Lower Limb</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Strong performer, small gains possible with more practice.</t>
-        </is>
-      </c>
+          <t>Thorax</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2061,19 +2041,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D16" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="E16" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F16" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -2083,11 +2063,7 @@
           <t>Lower Limb</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Doing very well overall, minor slips in application-based questions.</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2096,29 +2072,33 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>58</v>
       </c>
       <c r="E17" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F17" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lower Limb</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Upper Limb</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>On track, but should aim higher with focused practice.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2127,29 +2107,33 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C18" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E18" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="F18" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Neuroanatomy</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Abdomen</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Steady but needs more consistency across topics.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2158,26 +2142,26 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F19" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Thorax</t>
+          <t>Head &amp; Neck</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2189,26 +2173,26 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C20" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D20" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="F20" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Neuroanatomy</t>
+          <t>Thorax</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2220,26 +2204,26 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Lower Limb</t>
+          <t>Head &amp; Neck</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2251,29 +2235,29 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F22" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Encouraging progress, on the right track now.</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Head &amp; Neck</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2282,26 +2266,26 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C23" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D23" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E23" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F23" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Lower Limb</t>
+          <t>Neuroanatomy</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2313,26 +2297,26 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C24" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="D24" t="n">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="E24" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F24" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Thorax</t>
+          <t>Head &amp; Neck</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2344,26 +2328,26 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C25" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D25" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="E25" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F25" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Upper Limb</t>
+          <t>Neuroanatomy</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2375,26 +2359,26 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C26" t="n">
         <v>92</v>
       </c>
       <c r="D26" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E26" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F26" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Neuroanatomy</t>
+          <t>Upper Limb</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -2406,29 +2390,29 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C27" t="n">
+        <v>83</v>
+      </c>
+      <c r="D27" t="n">
         <v>85</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>82</v>
       </c>
-      <c r="E27" t="n">
-        <v>83</v>
-      </c>
       <c r="F27" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Solid understanding, encourage attempting harder problems.</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Neuroanatomy</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2437,33 +2421,29 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C28" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D28" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E28" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F28" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Lower Limb</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Strong performer, small gains possible with more practice.</t>
-        </is>
-      </c>
+          <t>Upper Limb</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2472,24 +2452,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="C29" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E29" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Abdomen</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2502,16 +2486,16 @@
         <v>63</v>
       </c>
       <c r="C30" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D30" t="n">
         <v>67</v>
       </c>
       <c r="E30" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F30" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2521,11 +2505,7 @@
           <t>Upper Limb</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Steady but needs more consistency across topics.</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2534,29 +2514,29 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C31" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D31" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E31" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F31" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Lower Limb</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Finding it difficult to keep pace, needs individual attention.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2637,24 +2617,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C2" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D2" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E2" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F2" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Nervous System</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -2664,33 +2648,29 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C3" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nervous System</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Strong performer, small gains possible with more practice.</t>
-        </is>
-      </c>
+          <t>Respiratory System</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2699,16 +2679,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C4" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D4" t="n">
+        <v>91</v>
+      </c>
+      <c r="E4" t="n">
         <v>84</v>
-      </c>
-      <c r="E4" t="n">
-        <v>86</v>
       </c>
       <c r="F4" t="n">
         <v>81</v>
@@ -2718,10 +2698,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Renal Physiology</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Respiratory System</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2730,19 +2714,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E5" t="n">
         <v>55</v>
       </c>
       <c r="F5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -2761,26 +2745,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C6" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D6" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E6" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F6" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Cardiovascular System</t>
+          <t>Respiratory System</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -2792,29 +2776,29 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n">
+        <v>27</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>34</v>
+      </c>
+      <c r="F7" t="n">
         <v>36</v>
       </c>
-      <c r="D7" t="n">
-        <v>38</v>
-      </c>
-      <c r="E7" t="n">
-        <v>30</v>
-      </c>
-      <c r="F7" t="n">
-        <v>28</v>
-      </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Struggling with fundamentals, needs remedial sessions.</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Cardiovascular System</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2823,26 +2807,26 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E8" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Endocrine System</t>
+          <t>Nervous System</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -2854,29 +2838,33 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" t="n">
         <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Nervous System</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Renal Physiology</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Very low scores across the board, please involve parents.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2885,19 +2873,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E10" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2907,11 +2895,7 @@
           <t>Respiratory System</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Encouraging progress, on the right track now.</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2920,26 +2904,26 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>70</v>
+      </c>
+      <c r="C11" t="n">
+        <v>62</v>
+      </c>
+      <c r="D11" t="n">
+        <v>65</v>
+      </c>
+      <c r="E11" t="n">
+        <v>69</v>
+      </c>
+      <c r="F11" t="n">
         <v>67</v>
       </c>
-      <c r="C11" t="n">
-        <v>66</v>
-      </c>
-      <c r="D11" t="n">
-        <v>60</v>
-      </c>
-      <c r="E11" t="n">
-        <v>58</v>
-      </c>
-      <c r="F11" t="n">
-        <v>64</v>
-      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Renal Physiology</t>
+          <t>Nervous System</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -2951,26 +2935,26 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
         <v>39</v>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E12" t="n">
         <v>32</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Respiratory System</t>
+          <t>Cardiovascular System</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2982,29 +2966,33 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E13" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F13" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Cardiovascular System</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Endocrine System</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Average performance — revision of basics recommended.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3013,29 +3001,33 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C14" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E14" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="F14" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Renal Physiology</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Respiratory System</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3044,24 +3036,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E15" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="F15" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Respiratory System</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -3071,29 +3067,29 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C16" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E16" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F16" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Endocrine System</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Strong performer, small gains possible with more practice.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3102,33 +3098,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C17" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E17" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F17" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Nervous System</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Steady but needs more consistency across topics.</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3137,26 +3125,26 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C18" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E18" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F18" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Nervous System</t>
+          <t>Cardiovascular System</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -3168,26 +3156,26 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C19" t="n">
+        <v>39</v>
+      </c>
+      <c r="D19" t="n">
+        <v>41</v>
+      </c>
+      <c r="E19" t="n">
+        <v>46</v>
+      </c>
+      <c r="F19" t="n">
         <v>42</v>
       </c>
-      <c r="D19" t="n">
-        <v>39</v>
-      </c>
-      <c r="E19" t="n">
-        <v>37</v>
-      </c>
-      <c r="F19" t="n">
-        <v>43</v>
-      </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Renal Physiology</t>
+          <t>Respiratory System</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3199,33 +3187,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F20" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Renal Physiology</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Below expectations — recommend extra classes after school.</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3234,33 +3214,29 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21" t="n">
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
+        <v>17</v>
+      </c>
+      <c r="F21" t="n">
         <v>10</v>
       </c>
-      <c r="F21" t="n">
-        <v>15</v>
-      </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Nervous System</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Serious concern — immediate intervention needed.</t>
-        </is>
-      </c>
+          <t>Endocrine System</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3269,26 +3245,26 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C22" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D22" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E22" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F22" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Cardiovascular System</t>
+          <t>Respiratory System</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3300,31 +3276,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C23" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D23" t="n">
         <v>62</v>
       </c>
       <c r="E23" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F23" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Nervous System</t>
+          <t>Renal Physiology</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Was doing well earlier, something seems to be affecting focus now.</t>
+          <t>Noticeable drop in performance, please check in at home.</t>
         </is>
       </c>
     </row>
@@ -3335,27 +3311,27 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C24" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D24" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E24" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="F24" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Unpredictable performance, may help to identify what's different on good days.</t>
+          <t>Inconsistent results — strong in some tests, weak in others.</t>
         </is>
       </c>
     </row>
@@ -3366,29 +3342,29 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C25" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D25" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F25" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Average performance — revision of basics recommended.</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Renal Physiology</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3397,10 +3373,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C26" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D26" t="n">
         <v>95</v>
@@ -3409,21 +3385,17 @@
         <v>91</v>
       </c>
       <c r="F26" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Nervous System</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Consistently excellent — ready for tougher challenges.</t>
-        </is>
-      </c>
+          <t>Cardiovascular System</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3432,28 +3404,24 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>81</v>
+      </c>
+      <c r="C27" t="n">
+        <v>75</v>
+      </c>
+      <c r="D27" t="n">
         <v>82</v>
       </c>
-      <c r="C27" t="n">
+      <c r="E27" t="n">
+        <v>82</v>
+      </c>
+      <c r="F27" t="n">
         <v>81</v>
       </c>
-      <c r="D27" t="n">
-        <v>81</v>
-      </c>
-      <c r="E27" t="n">
-        <v>79</v>
-      </c>
-      <c r="F27" t="n">
-        <v>88</v>
-      </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Cardiovascular System</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -3463,29 +3431,29 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>89</v>
+      </c>
+      <c r="C28" t="n">
+        <v>90</v>
+      </c>
+      <c r="D28" t="n">
+        <v>83</v>
+      </c>
+      <c r="E28" t="n">
+        <v>92</v>
+      </c>
+      <c r="F28" t="n">
         <v>82</v>
       </c>
-      <c r="C28" t="n">
-        <v>85</v>
-      </c>
-      <c r="D28" t="n">
-        <v>87</v>
-      </c>
-      <c r="E28" t="n">
-        <v>79</v>
-      </c>
-      <c r="F28" t="n">
-        <v>85</v>
-      </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Cardiovascular System</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3494,31 +3462,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C29" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D29" t="n">
         <v>61</v>
       </c>
       <c r="E29" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F29" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Nervous System</t>
+          <t>Renal Physiology</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>On track, but should aim higher with focused practice.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -3529,33 +3497,29 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C30" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D30" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E30" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F30" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Nervous System</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Steady but needs more consistency across topics.</t>
-        </is>
-      </c>
+          <t>Endocrine System</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3564,28 +3528,24 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C31" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D31" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E31" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F31" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Endocrine System</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
@@ -3667,19 +3627,19 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C2" t="n">
+        <v>48</v>
+      </c>
+      <c r="D2" t="n">
         <v>46</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>46</v>
       </c>
-      <c r="D2" t="n">
-        <v>48</v>
-      </c>
-      <c r="E2" t="n">
-        <v>48</v>
-      </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -3698,28 +3658,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Carbohydrate Metabolism</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -3735,22 +3691,18 @@
         <v>40</v>
       </c>
       <c r="D4" t="n">
+        <v>39</v>
+      </c>
+      <c r="E4" t="n">
         <v>40</v>
       </c>
-      <c r="E4" t="n">
-        <v>38</v>
-      </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Molecular Biology</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -3763,21 +3715,25 @@
         <v>33</v>
       </c>
       <c r="C5" t="n">
+        <v>31</v>
+      </c>
+      <c r="D5" t="n">
+        <v>32</v>
+      </c>
+      <c r="E5" t="n">
+        <v>35</v>
+      </c>
+      <c r="F5" t="n">
         <v>30</v>
       </c>
-      <c r="D5" t="n">
-        <v>28</v>
-      </c>
-      <c r="E5" t="n">
-        <v>28</v>
-      </c>
-      <c r="F5" t="n">
-        <v>32</v>
-      </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Molecular Biology</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -3787,24 +3743,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" t="n">
         <v>34</v>
       </c>
       <c r="E6" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Carbohydrate Metabolism</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -3814,19 +3774,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
         <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -3841,29 +3801,33 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Carbohydrate Metabolism</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Vitamins</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Struggling with fundamentals, needs remedial sessions.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3875,26 +3839,22 @@
         <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Serious concern — immediate intervention needed.</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3903,28 +3863,24 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>36</v>
+      </c>
+      <c r="C10" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" t="n">
+        <v>31</v>
+      </c>
+      <c r="E10" t="n">
         <v>33</v>
       </c>
-      <c r="C10" t="n">
-        <v>30</v>
-      </c>
-      <c r="D10" t="n">
-        <v>33</v>
-      </c>
-      <c r="E10" t="n">
-        <v>30</v>
-      </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Vitamins</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -3937,30 +3893,26 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D11" t="n">
+        <v>24</v>
+      </c>
+      <c r="E11" t="n">
         <v>25</v>
       </c>
-      <c r="D11" t="n">
-        <v>25</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>23</v>
       </c>
-      <c r="F11" t="n">
-        <v>22</v>
-      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Molecular Biology</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Noticeable drop in performance, please check in at home.</t>
-        </is>
-      </c>
+          <t>Carbohydrate Metabolism</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3969,24 +3921,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Enzymes</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -3996,28 +3952,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" t="n">
+        <v>32</v>
+      </c>
+      <c r="D13" t="n">
+        <v>31</v>
+      </c>
+      <c r="E13" t="n">
+        <v>32</v>
+      </c>
+      <c r="F13" t="n">
         <v>36</v>
       </c>
-      <c r="D13" t="n">
-        <v>34</v>
-      </c>
-      <c r="E13" t="n">
-        <v>34</v>
-      </c>
-      <c r="F13" t="n">
-        <v>31</v>
-      </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Protein Metabolism</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -4027,29 +3979,29 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E14" t="n">
         <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Consistently excellent — ready for tougher challenges.</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vitamins</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4061,23 +4013,23 @@
         <v>40</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
         <v>44</v>
       </c>
       <c r="E15" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Vitamins</t>
+          <t>Molecular Biology</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -4089,19 +4041,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C16" t="n">
+        <v>40</v>
+      </c>
+      <c r="D16" t="n">
+        <v>42</v>
+      </c>
+      <c r="E16" t="n">
+        <v>45</v>
+      </c>
+      <c r="F16" t="n">
         <v>39</v>
-      </c>
-      <c r="D16" t="n">
-        <v>40</v>
-      </c>
-      <c r="E16" t="n">
-        <v>42</v>
-      </c>
-      <c r="F16" t="n">
-        <v>41</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -4123,16 +4075,16 @@
         <v>28</v>
       </c>
       <c r="C17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D17" t="n">
         <v>31</v>
       </c>
-      <c r="D17" t="n">
-        <v>34</v>
-      </c>
       <c r="E17" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F17" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -4147,24 +4099,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>29</v>
       </c>
       <c r="E18" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F18" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Vitamins</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -4174,29 +4130,33 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
         <v>22</v>
       </c>
       <c r="D19" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E19" t="n">
         <v>21</v>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Enzymes</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Protein Metabolism</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Below expectations — recommend extra classes after school.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4205,33 +4165,29 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>17</v>
+      </c>
+      <c r="C20" t="n">
+        <v>20</v>
+      </c>
+      <c r="D20" t="n">
+        <v>20</v>
+      </c>
+      <c r="E20" t="n">
         <v>19</v>
       </c>
-      <c r="C20" t="n">
-        <v>18</v>
-      </c>
-      <c r="D20" t="n">
-        <v>24</v>
-      </c>
-      <c r="E20" t="n">
-        <v>21</v>
-      </c>
       <c r="F20" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Molecular Biology</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Finding it difficult to keep pace, needs individual attention.</t>
-        </is>
-      </c>
+          <t>Vitamins</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4240,25 +4196,33 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" t="n">
         <v>6</v>
       </c>
-      <c r="F21" t="n">
-        <v>2</v>
-      </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Protein Metabolism</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Needs urgent academic support, at risk of failing.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4267,24 +4231,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C22" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D22" t="n">
+        <v>35</v>
+      </c>
+      <c r="E22" t="n">
+        <v>35</v>
+      </c>
+      <c r="F22" t="n">
         <v>34</v>
       </c>
-      <c r="E22" t="n">
-        <v>30</v>
-      </c>
-      <c r="F22" t="n">
-        <v>31</v>
-      </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Vitamins</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -4294,28 +4262,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E23" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F23" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Vitamins</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -4325,26 +4289,26 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C24" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F24" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Carbohydrate Metabolism</t>
+          <t>Protein Metabolism</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -4356,28 +4320,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C25" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E25" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F25" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Protein Metabolism</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -4387,26 +4347,26 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D26" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E26" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F26" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Vitamins</t>
+          <t>Enzymes</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4422,16 +4382,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C27" t="n">
+        <v>45</v>
+      </c>
+      <c r="D27" t="n">
         <v>43</v>
       </c>
-      <c r="D27" t="n">
-        <v>39</v>
-      </c>
       <c r="E27" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F27" t="n">
         <v>41</v>
@@ -4453,33 +4413,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C28" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D28" t="n">
+        <v>40</v>
+      </c>
+      <c r="E28" t="n">
         <v>43</v>
       </c>
-      <c r="E28" t="n">
-        <v>42</v>
-      </c>
       <c r="F28" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Protein Metabolism</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Solid understanding, encourage attempting harder problems.</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4491,26 +4443,26 @@
         <v>29</v>
       </c>
       <c r="C29" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E29" t="n">
         <v>26</v>
       </c>
       <c r="F29" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Steady but needs more consistency across topics.</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Enzymes</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4519,26 +4471,26 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C30" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D30" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E30" t="n">
         <v>31</v>
       </c>
       <c r="F30" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Protein Metabolism</t>
+          <t>Carbohydrate Metabolism</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4550,29 +4502,29 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C31" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D31" t="n">
         <v>19</v>
       </c>
       <c r="E31" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F31" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Below expectations — recommend extra classes after school.</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Carbohydrate Metabolism</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4653,31 +4605,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C2" t="n">
+        <v>97</v>
+      </c>
+      <c r="D2" t="n">
+        <v>98</v>
+      </c>
+      <c r="E2" t="n">
         <v>93</v>
       </c>
-      <c r="D2" t="n">
-        <v>88</v>
-      </c>
-      <c r="E2" t="n">
-        <v>97</v>
-      </c>
       <c r="F2" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Cell Injury</t>
+          <t>Inflammation</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Exceptional performance, keep up this standard.</t>
+          <t>Consistently excellent — ready for tougher challenges.</t>
         </is>
       </c>
     </row>
@@ -4688,19 +4640,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C3" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D3" t="n">
+        <v>96</v>
+      </c>
+      <c r="E3" t="n">
         <v>87</v>
       </c>
-      <c r="E3" t="n">
-        <v>78</v>
-      </c>
       <c r="F3" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -4712,7 +4664,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Strong performer, small gains possible with more practice.</t>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
         </is>
       </c>
     </row>
@@ -4723,26 +4675,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C4" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D4" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="E4" t="n">
+        <v>85</v>
+      </c>
+      <c r="F4" t="n">
         <v>87</v>
       </c>
-      <c r="F4" t="n">
-        <v>90</v>
-      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hematology Basics</t>
+          <t>Neoplasia</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -4758,24 +4710,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C5" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E5" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Hematology Basics</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -4789,31 +4745,27 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C6" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E6" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Cell Injury</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>On track, but should aim higher with focused practice.</t>
         </is>
       </c>
     </row>
@@ -4824,27 +4776,31 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>24</v>
+      </c>
+      <c r="C7" t="n">
         <v>28</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>30</v>
       </c>
-      <c r="D7" t="n">
-        <v>33</v>
-      </c>
       <c r="E7" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Inflammation</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Struggling with fundamentals, needs remedial sessions.</t>
+          <t>Finding it difficult to keep pace, needs individual attention.</t>
         </is>
       </c>
     </row>
@@ -4855,31 +4811,31 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>51</v>
+      </c>
+      <c r="C8" t="n">
         <v>41</v>
       </c>
-      <c r="C8" t="n">
-        <v>39</v>
-      </c>
       <c r="D8" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E8" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hematology Basics</t>
+          <t>Inflammation</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Struggling with fundamentals, needs remedial sessions.</t>
+          <t>Finding it difficult to keep pace, needs individual attention.</t>
         </is>
       </c>
     </row>
@@ -4890,31 +4846,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" t="n">
         <v>12</v>
       </c>
-      <c r="D9" t="n">
-        <v>13</v>
-      </c>
-      <c r="E9" t="n">
-        <v>10</v>
-      </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Inflammation</t>
+          <t>Hematology Basics</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Needs urgent academic support, at risk of failing.</t>
+          <t>Very low scores across the board, please involve parents.</t>
         </is>
       </c>
     </row>
@@ -4925,16 +4881,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C10" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D10" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E10" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F10" t="n">
         <v>81</v>
@@ -4942,7 +4898,11 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Cell Injury</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>Great turnaround this term, keep the momentum going!</t>
@@ -4956,31 +4916,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Cell Injury</t>
+          <t>Hematology Basics</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Was doing well earlier, something seems to be affecting focus now.</t>
+          <t>Noticeable drop in performance, please check in at home.</t>
         </is>
       </c>
     </row>
@@ -4991,31 +4951,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="C12" t="n">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="E12" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="F12" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hematology Basics</t>
+          <t>Inflammation</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Ups and downs need to be understood — talk to student directly.</t>
+          <t>Inconsistent results — strong in some tests, weak in others.</t>
         </is>
       </c>
     </row>
@@ -5026,28 +4986,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E13" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Neoplasia</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -5061,27 +5017,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E14" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F14" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Cell Injury</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
+          <t>Consistently excellent — ready for tougher challenges.</t>
         </is>
       </c>
     </row>
@@ -5092,31 +5052,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C15" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E15" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="F15" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Cell Injury</t>
+          <t>Hematology Basics</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Strong performer, small gains possible with more practice.</t>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
         </is>
       </c>
     </row>
@@ -5127,19 +5087,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C16" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E16" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F16" t="n">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -5162,31 +5122,27 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C17" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E17" t="n">
         <v>55</v>
       </c>
       <c r="F17" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Neoplasia</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>Steady but needs more consistency across topics.</t>
         </is>
       </c>
     </row>
@@ -5197,31 +5153,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C18" t="n">
+        <v>60</v>
+      </c>
+      <c r="D18" t="n">
         <v>59</v>
       </c>
-      <c r="D18" t="n">
-        <v>61</v>
-      </c>
       <c r="E18" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F18" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Hematology Basics</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Steady but needs more consistency across topics.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -5232,19 +5184,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="C19" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D19" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E19" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F19" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -5267,27 +5219,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D20" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E20" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F20" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Hematology Basics</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Below expectations — recommend extra classes after school.</t>
+          <t>Finding it difficult to keep pace, needs individual attention.</t>
         </is>
       </c>
     </row>
@@ -5298,28 +5254,24 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>11</v>
+      </c>
+      <c r="C21" t="n">
+        <v>12</v>
+      </c>
+      <c r="D21" t="n">
         <v>14</v>
       </c>
-      <c r="C21" t="n">
-        <v>13</v>
-      </c>
-      <c r="D21" t="n">
-        <v>9</v>
-      </c>
       <c r="E21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F21" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Hematology Basics</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Very low scores across the board, please involve parents.</t>
@@ -5333,31 +5285,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C22" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D22" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E22" t="n">
         <v>83</v>
       </c>
       <c r="F22" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Cell Injury</t>
+          <t>Neoplasia</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Great turnaround this term, keep the momentum going!</t>
+          <t>Encouraging progress, on the right track now.</t>
         </is>
       </c>
     </row>
@@ -5368,31 +5320,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C23" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D23" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E23" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F23" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Cell Injury</t>
+          <t>Hematology Basics</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Was doing well earlier, something seems to be affecting focus now.</t>
+          <t>Noticeable drop in performance, please check in at home.</t>
         </is>
       </c>
     </row>
@@ -5403,27 +5355,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="C24" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D24" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E24" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="F24" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Neoplasia</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Unpredictable performance, may help to identify what's different on good days.</t>
+          <t>Inconsistent results — strong in some tests, weak in others.</t>
         </is>
       </c>
     </row>
@@ -5434,31 +5390,27 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>53</v>
+      </c>
+      <c r="C25" t="n">
+        <v>60</v>
+      </c>
+      <c r="D25" t="n">
+        <v>55</v>
+      </c>
+      <c r="E25" t="n">
         <v>61</v>
       </c>
-      <c r="C25" t="n">
-        <v>69</v>
-      </c>
-      <c r="D25" t="n">
-        <v>58</v>
-      </c>
-      <c r="E25" t="n">
-        <v>69</v>
-      </c>
       <c r="F25" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Hematology Basics</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>On track, but should aim higher with focused practice.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -5469,24 +5421,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C26" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D26" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E26" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F26" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Neoplasia</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>Exceptional performance, keep up this standard.</t>
@@ -5500,31 +5456,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C27" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D27" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E27" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F27" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Hematology Basics</t>
+          <t>Neoplasia</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Doing very well overall, minor slips in application-based questions.</t>
+          <t>Strong performer, small gains possible with more practice.</t>
         </is>
       </c>
     </row>
@@ -5535,28 +5491,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C28" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D28" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E28" t="n">
         <v>90</v>
       </c>
       <c r="F28" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Hematology Basics</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Strong performer, small gains possible with more practice.</t>
@@ -5570,31 +5522,27 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C29" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D29" t="n">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="E29" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F29" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Inflammation</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>On track, but should aim higher with focused practice.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -5605,26 +5553,26 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>65</v>
+      </c>
+      <c r="C30" t="n">
+        <v>58</v>
+      </c>
+      <c r="D30" t="n">
+        <v>69</v>
+      </c>
+      <c r="E30" t="n">
+        <v>68</v>
+      </c>
+      <c r="F30" t="n">
         <v>59</v>
       </c>
-      <c r="C30" t="n">
-        <v>69</v>
-      </c>
-      <c r="D30" t="n">
-        <v>59</v>
-      </c>
-      <c r="E30" t="n">
-        <v>69</v>
-      </c>
-      <c r="F30" t="n">
-        <v>63</v>
-      </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Hematology Basics</t>
+          <t>Neoplasia</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -5640,28 +5588,24 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C31" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D31" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E31" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F31" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Hematology Basics</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Struggling with fundamentals, needs remedial sessions.</t>

--- a/samples/Sample_2_For_MBBS_College_Lecturer.xlsx
+++ b/samples/Sample_2_For_MBBS_College_Lecturer.xlsx
@@ -9,10 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SETUP" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STUDENTS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internal Assessment 1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internal Assessment 2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practical Exam 1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="University Sendup" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MBBS-Y2-Internal Assessment 1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MBBS-Y2-Internal Assessment 2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MBBS-Y2-Practical Exam 1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MBBS-Y2-University Sendup" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
@@ -525,7 +525,6 @@
           <t>Section</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -633,7 +632,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Internal Assessment 1</t>
+          <t>MBBS-Y2-Internal Assessment 1</t>
         </is>
       </c>
     </row>
@@ -702,7 +701,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Internal Assessment 2</t>
+          <t>MBBS-Y2-Internal Assessment 2</t>
         </is>
       </c>
     </row>
@@ -771,7 +770,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Practical Exam 1</t>
+          <t>MBBS-Y2-Practical Exam 1</t>
         </is>
       </c>
     </row>
@@ -840,7 +839,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>University Sendup</t>
+          <t>MBBS-Y2-University Sendup</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1667,6 @@
           <t>Upper Limb</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1699,7 +1697,6 @@
           <t>Head &amp; Neck</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1725,8 +1722,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1757,7 +1752,6 @@
           <t>Head &amp; Neck</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1783,7 +1777,6 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Below expectations — recommend extra classes after school.</t>
@@ -1819,7 +1812,6 @@
           <t>Abdomen</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1845,8 +1837,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1877,7 +1867,6 @@
           <t>Thorax</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1908,7 +1897,6 @@
           <t>Abdomen</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1939,7 +1927,6 @@
           <t>Lower Limb</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1965,7 +1952,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -2001,7 +1987,6 @@
           <t>Thorax</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2032,7 +2017,6 @@
           <t>Thorax</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2063,7 +2047,6 @@
           <t>Lower Limb</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2164,7 +2147,6 @@
           <t>Head &amp; Neck</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2195,7 +2177,6 @@
           <t>Thorax</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2226,7 +2207,6 @@
           <t>Head &amp; Neck</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2257,7 +2237,6 @@
           <t>Head &amp; Neck</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2288,7 +2267,6 @@
           <t>Neuroanatomy</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2319,7 +2297,6 @@
           <t>Head &amp; Neck</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2350,7 +2327,6 @@
           <t>Neuroanatomy</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2381,7 +2357,6 @@
           <t>Upper Limb</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2412,7 +2387,6 @@
           <t>Neuroanatomy</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2443,7 +2417,6 @@
           <t>Upper Limb</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2474,7 +2447,6 @@
           <t>Abdomen</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2505,7 +2477,6 @@
           <t>Upper Limb</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2531,7 +2502,6 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Finding it difficult to keep pace, needs individual attention.</t>
@@ -2639,7 +2609,6 @@
           <t>Nervous System</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2670,7 +2639,6 @@
           <t>Respiratory System</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2736,7 +2704,6 @@
           <t>Endocrine System</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2767,7 +2734,6 @@
           <t>Respiratory System</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2798,7 +2764,6 @@
           <t>Cardiovascular System</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2829,7 +2794,6 @@
           <t>Nervous System</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2895,7 +2859,6 @@
           <t>Respiratory System</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2926,7 +2889,6 @@
           <t>Nervous System</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2957,7 +2919,6 @@
           <t>Cardiovascular System</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3058,7 +3019,6 @@
           <t>Respiratory System</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3084,7 +3044,6 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Strong performer, small gains possible with more practice.</t>
@@ -3115,8 +3074,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3147,7 +3104,6 @@
           <t>Cardiovascular System</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3178,7 +3134,6 @@
           <t>Respiratory System</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3204,8 +3159,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3236,7 +3189,6 @@
           <t>Endocrine System</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3267,7 +3219,6 @@
           <t>Respiratory System</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3328,7 +3279,6 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Inconsistent results — strong in some tests, weak in others.</t>
@@ -3364,7 +3314,6 @@
           <t>Renal Physiology</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3395,7 +3344,6 @@
           <t>Cardiovascular System</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3421,8 +3369,6 @@
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3448,7 +3394,6 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Doing very well overall, minor slips in application-based questions.</t>
@@ -3519,7 +3464,6 @@
           <t>Endocrine System</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3545,8 +3489,6 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3649,7 +3591,6 @@
           <t>Enzymes</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3675,8 +3616,6 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3702,8 +3641,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3734,7 +3671,6 @@
           <t>Molecular Biology</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3765,7 +3701,6 @@
           <t>Carbohydrate Metabolism</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3791,8 +3726,6 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3853,8 +3786,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3880,8 +3811,6 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3912,7 +3841,6 @@
           <t>Carbohydrate Metabolism</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3943,7 +3871,6 @@
           <t>Enzymes</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3969,8 +3896,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4001,7 +3926,6 @@
           <t>Vitamins</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4032,7 +3956,6 @@
           <t>Molecular Biology</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4063,7 +3986,6 @@
           <t>Protein Metabolism</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4089,8 +4011,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4121,7 +4041,6 @@
           <t>Vitamins</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4187,7 +4106,6 @@
           <t>Vitamins</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4253,7 +4171,6 @@
           <t>Vitamins</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4279,8 +4196,6 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4311,7 +4226,6 @@
           <t>Protein Metabolism</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4337,8 +4251,6 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4404,7 +4316,6 @@
           <t>Molecular Biology</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4430,8 +4341,6 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4462,7 +4371,6 @@
           <t>Enzymes</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4493,7 +4401,6 @@
           <t>Carbohydrate Metabolism</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4524,7 +4431,6 @@
           <t>Carbohydrate Metabolism</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4762,7 +4668,6 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -5003,7 +4908,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -5139,7 +5043,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -5170,7 +5073,6 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -5271,7 +5173,6 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Very low scores across the board, please involve parents.</t>
@@ -5407,7 +5308,6 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -5508,7 +5408,6 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Strong performer, small gains possible with more practice.</t>
@@ -5539,7 +5438,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -5605,7 +5503,6 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Struggling with fundamentals, needs remedial sessions.</t>
